--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/23,07,26 ПОКОМ КИ/дв 23,07,26 днрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/23,07,26 ПОКОМ КИ/дв 23,07,26 днрсч пок ки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\23,07,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B0F166-DD42-4896-B461-EA3BA68311F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5BCA66-5B26-4775-8125-6810A3212075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -800,12 +800,12 @@
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="S5" s="4">
         <f t="shared" ref="S5" si="1">SUM(S6:S500)</f>
-        <v>-5061.8571428571431</v>
+        <v>-5876.3571428571431</v>
       </c>
       <c r="T5" s="21">
         <f t="shared" ref="T5" si="2">SUM(T6:T500)</f>
-        <v>4500</v>
+        <v>4700</v>
       </c>
       <c r="U5" s="4">
         <f t="shared" si="0"/>
@@ -8254,7 +8254,10 @@
       <c r="R64" s="1">
         <v>433.66716328480021</v>
       </c>
-      <c r="S64" s="1"/>
+      <c r="S64" s="1">
+        <f>-172.2/G64</f>
+        <v>-430.49999999999994</v>
+      </c>
       <c r="T64" s="20"/>
       <c r="U64" s="1">
         <f t="shared" si="6"/>
@@ -8270,11 +8273,11 @@
       </c>
       <c r="X64" s="1">
         <f t="shared" si="8"/>
-        <v>10.509999999999998</v>
+        <v>5.1555223880597003</v>
       </c>
       <c r="Y64" s="1">
         <f t="shared" si="9"/>
-        <v>7.9436214338905486</v>
+        <v>2.5891438219502514</v>
       </c>
       <c r="Z64" s="1">
         <v>83.4</v>
@@ -9999,7 +10002,10 @@
       <c r="R80" s="1">
         <v>381.44</v>
       </c>
-      <c r="S80" s="1"/>
+      <c r="S80" s="1">
+        <f>-134.4/G80</f>
+        <v>-384.00000000000006</v>
+      </c>
       <c r="T80" s="20"/>
       <c r="U80" s="1">
         <f t="shared" si="26"/>
@@ -10015,11 +10021,11 @@
       </c>
       <c r="X80" s="1">
         <f t="shared" si="28"/>
-        <v>12</v>
+        <v>1.2737430167597741</v>
       </c>
       <c r="Y80" s="1">
         <f t="shared" si="29"/>
-        <v>11.548603351955308</v>
+        <v>0.82234636871508227</v>
       </c>
       <c r="Z80" s="1">
         <v>40.6</v>
@@ -11018,7 +11024,7 @@
       </c>
       <c r="S89" s="1"/>
       <c r="T89" s="20">
-        <v>4500</v>
+        <v>4700</v>
       </c>
       <c r="U89" s="1">
         <f t="shared" si="26"/>
@@ -11031,11 +11037,11 @@
       </c>
       <c r="X89" s="1">
         <f t="shared" si="28"/>
-        <v>20.759429568774944</v>
+        <v>21.143361849263584</v>
       </c>
       <c r="Y89" s="1">
         <f t="shared" si="29"/>
-        <v>20.759429568774944</v>
+        <v>21.143361849263584</v>
       </c>
       <c r="Z89" s="1">
         <v>627.79740000000004</v>
